--- a/artfynd/A 36998-2025 artfynd.xlsx
+++ b/artfynd/A 36998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16847630</v>
+        <v>16847632</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612184.5675153206</v>
+        <v>612353</v>
       </c>
       <c r="R2" t="n">
-        <v>7165828.712015281</v>
+        <v>7165871</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-09-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gransumpskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>lövrik granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,117 +774,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>16847632</v>
-      </c>
-      <c r="B3" t="n">
-        <v>99882</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1365</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Coptidium lapponicum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Åsvattenbäcken, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>612353</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7165871</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2014-09-02</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2014-09-02</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>lövrik granskog</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Niina Sallmén</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Niina Sallmén, sofia nordin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
